--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.36380562829453</v>
+        <v>5.096618414597861</v>
       </c>
       <c r="D2" t="n">
-        <v>35.96144427156022</v>
+        <v>5.843734694128536</v>
       </c>
       <c r="E2" t="n">
-        <v>12.91867983997934</v>
+        <v>2.099285473996643</v>
       </c>
       <c r="F2" t="n">
-        <v>13.0979583393647</v>
+        <v>2.128418230146763</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.23763852423925</v>
+        <v>1.663616260188878</v>
       </c>
       <c r="D3" t="n">
-        <v>9.843072968417326</v>
+        <v>1.599499357367816</v>
       </c>
       <c r="E3" t="n">
-        <v>12.91867983997934</v>
+        <v>2.099285473996643</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0979583393647</v>
+        <v>2.128418230146763</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.06120172587055</v>
+        <v>7.647445280453964</v>
       </c>
       <c r="D4" t="n">
-        <v>47.10584212352499</v>
+        <v>7.654699345072812</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91867983997934</v>
+        <v>2.099285473996643</v>
       </c>
       <c r="F4" t="n">
-        <v>13.0979583393647</v>
+        <v>2.128418230146763</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.62704641040568</v>
+        <v>4.976895041690923</v>
       </c>
       <c r="D5" t="n">
-        <v>29.9849859051434</v>
+        <v>4.872560209585803</v>
       </c>
       <c r="E5" t="n">
-        <v>12.91867983997934</v>
+        <v>2.099285473996643</v>
       </c>
       <c r="F5" t="n">
-        <v>13.0979583393647</v>
+        <v>2.128418230146763</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.54734975135712</v>
+        <v>7.076444334595532</v>
       </c>
       <c r="D6" t="n">
-        <v>43.24520475362643</v>
+        <v>7.027345772464296</v>
       </c>
       <c r="E6" t="n">
-        <v>12.91867983997934</v>
+        <v>2.099285473996643</v>
       </c>
       <c r="F6" t="n">
-        <v>13.0979583393647</v>
+        <v>2.128418230146763</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
